--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -60,7 +60,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
@@ -277,6 +277,126 @@
         <bgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE0E0"/>
+        <bgColor rgb="00FDE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0042A5F5"/>
+        <bgColor rgb="0042A5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066BB6A"/>
+        <bgColor rgb="0066BB6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F06292"/>
+        <bgColor rgb="00F06292"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090CAF9"/>
+        <bgColor rgb="0090CAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC407A"/>
+        <bgColor rgb="00EC407A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0064B5F6"/>
+        <bgColor rgb="0064B5F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFECB3"/>
+        <bgColor rgb="00FFECB3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE082"/>
+        <bgColor rgb="00FFE082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD54F"/>
+        <bgColor rgb="00FFD54F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F48FB1"/>
+        <bgColor rgb="00F48FB1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCA28"/>
+        <bgColor rgb="00FFCA28"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0081C784"/>
+        <bgColor rgb="0081C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BBD0"/>
+        <bgColor rgb="00F8BBD0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -299,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -361,6 +481,26 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27259,2032 +27399,2032 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="47" t="inlineStr">
         <is>
           <t>MS C - 1</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="E2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="G2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="I2" s="52" t="inlineStr">
         <is>
           <t>MS A - 1</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr">
+      <c r="J2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="K2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="L2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N2" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="O2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="Q2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="R2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="S2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="T2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="U2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="V2" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="X2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="Y2" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AB2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AC2" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="AD2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AE2" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AF2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AG2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AH2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 5</t>
+        </is>
+      </c>
+      <c r="AI2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AK2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AM2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AN2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="AO2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="AP2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 5</t>
+        </is>
+      </c>
+      <c r="AQ2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 5</t>
+        </is>
+      </c>
+      <c r="AR2" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="E3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="G3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H3" s="52" t="inlineStr">
         <is>
           <t>MS A - 1</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr">
+      <c r="I3" s="52" t="inlineStr">
         <is>
           <t>MS A - 1</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="J3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="K3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N3" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="O3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="R3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="S3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="T3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="U3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="V3" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="X3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="Y3" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AB3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC3" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 5</t>
+        </is>
+      </c>
+      <c r="AD3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE3" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AF3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AG3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AH3" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ3" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK3" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AM3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AN3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AO3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="AP3" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
+        </is>
+      </c>
+      <c r="AQ3" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>MS C - 2</t>
         </is>
       </c>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="G4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="K4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L4" s="52" t="inlineStr">
         <is>
           <t>MS A - 2</t>
         </is>
       </c>
-      <c r="H2" s="31" t="inlineStr">
+      <c r="M4" s="52" t="inlineStr">
         <is>
           <t>MS A - 2</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="N4" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="O4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="R4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="S4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="V4" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="X4" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="Y4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AB4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AF4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AH4" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ4" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK4" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AM4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AN4" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AO4" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="AP4" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AQ4" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="J2" s="31" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="K5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N5" s="52" t="inlineStr">
         <is>
           <t>MS A - 3</t>
         </is>
       </c>
-      <c r="K2" s="31" t="inlineStr">
+      <c r="O5" s="52" t="inlineStr">
         <is>
           <t>MS A - 3</t>
         </is>
       </c>
-      <c r="L2" s="33" t="inlineStr">
+      <c r="P5" s="48" t="inlineStr">
         <is>
           <t>MS B - 2</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="N2" s="32" t="inlineStr">
+      <c r="Q5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="R5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="S5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="V5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="X5" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AB5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE5" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AF5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG5" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AH5" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK5" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AM5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AN5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AO5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+      <c r="AP5" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AQ5" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="O2" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="P2" s="32" t="inlineStr">
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="K6" s="50" t="inlineStr">
         <is>
           <t>MD A - 2</t>
         </is>
       </c>
-      <c r="Q2" s="34" t="inlineStr">
+      <c r="L6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="O6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="S6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U6" s="55" t="inlineStr">
         <is>
           <t>MS V - 1</t>
         </is>
       </c>
-      <c r="R2" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="S2" s="32" t="inlineStr">
+      <c r="V6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="X6" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="Y6" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA6" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AB6" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD6" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AH6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI6" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ6" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AM6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AN6" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AO6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="AQ6" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="K7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N7" s="50" t="inlineStr">
         <is>
           <t>MD A - 3</t>
         </is>
       </c>
-      <c r="T2" s="34" t="inlineStr">
+      <c r="O7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="S7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="V7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W7" s="55" t="inlineStr">
         <is>
           <t>MS V - 2</t>
         </is>
       </c>
-      <c r="U2" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="V2" s="33" t="inlineStr">
+      <c r="X7" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA7" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AB7" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD7" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG7" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+      <c r="AH7" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI7" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ7" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL7" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AM7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AN7" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AO7" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="G8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="K8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="N8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="O8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="P8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="S8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="V8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="X8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="Y8" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="AB8" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD8" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG8" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AH8" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AI8" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ8" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK8" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL8" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AM8" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AN8" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AO8" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="G9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="K9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="L9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="O9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="P9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R9" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="S9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T9" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="V9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="W9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="X9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="Y9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Z9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="AB9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AF9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AG9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AH9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="AI9" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="AJ9" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AK9" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL9" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AM9" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AN9" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AO9" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="G10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="L10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="M10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O10" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="P10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R10" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="S10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="V10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="W10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="X10" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="Y10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="Z10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AB10" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AC10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AD10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AF10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AG10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AH10" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="AI10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AJ10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 4</t>
+        </is>
+      </c>
+      <c r="AK10" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AL10" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AM10" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AO10" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="L11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="M11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+      <c r="N11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O11" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="P11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Q11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="R11" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="S11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="U11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="V11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="W11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="X11" s="48" t="inlineStr">
         <is>
           <t>MS B - 6</t>
         </is>
       </c>
-      <c r="W2" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="X2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="Y2" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="Z2" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA2" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 5</t>
-        </is>
-      </c>
-      <c r="AB2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AC2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AD2" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AE2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AF2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AG2" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AH2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AI2" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AJ2" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 5</t>
-        </is>
-      </c>
-      <c r="AK2" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 5</t>
-        </is>
-      </c>
-      <c r="AL2" s="38" t="inlineStr">
+      <c r="Y11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="Z11" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="AA11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 5</t>
+        </is>
+      </c>
+      <c r="AB11" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AC11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AD11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AE11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="AF11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AG11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AI11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AL11" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AM11" s="62" t="inlineStr">
         <is>
           <t>WD A - 2</t>
         </is>
       </c>
-      <c r="AM2" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AN2" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 4</t>
-        </is>
-      </c>
-      <c r="AO2" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AP2" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AQ2" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 4</t>
-        </is>
-      </c>
-      <c r="AR2" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E3" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="F3" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I3" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="J3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="L3" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="N3" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="O3" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="P3" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Q3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="R3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="S3" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="T3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="U3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="V3" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="W3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="X3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="Y3" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="Z3" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA3" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AC3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AD3" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AE3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AF3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AG3" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AH3" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AI3" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AJ3" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK3" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AL3" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AM3" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AN3" s="41" t="inlineStr">
+      <c r="AO11" s="61" t="inlineStr">
         <is>
           <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AO3" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AP3" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AQ3" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 4</t>
-        </is>
-      </c>
-      <c r="AR3" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="F4" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I4" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="L4" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="N4" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="O4" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="P4" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Q4" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="R4" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="S4" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="T4" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="U4" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="V4" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="W4" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="X4" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 1</t>
-        </is>
-      </c>
-      <c r="Y4" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z4" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA4" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB4" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AC4" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AD4" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AE4" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AF4" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AG4" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AH4" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 5</t>
-        </is>
-      </c>
-      <c r="AI4" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AJ4" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AK4" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AL4" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AM4" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AN4" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AO4" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
-        </is>
-      </c>
-      <c r="AP4" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="AQ4" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="F5" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="L5" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="N5" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="O5" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="P5" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Q5" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 6</t>
-        </is>
-      </c>
-      <c r="R5" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S5" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="T5" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="U5" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="V5" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="W5" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="X5" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="Y5" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z5" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA5" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB5" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AC5" s="35" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AD5" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AE5" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AF5" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AG5" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AH5" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AI5" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AJ5" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AK5" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AL5" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="AM5" s="39" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AN5" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AO5" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="AP5" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="F6" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I6" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J6" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="L6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M6" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="N6" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="O6" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q6" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="R6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S6" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="T6" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="U6" s="34" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="V6" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="W6" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 5</t>
-        </is>
-      </c>
-      <c r="X6" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="Y6" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z6" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA6" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB6" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC6" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AD6" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AE6" s="37" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AF6" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AG6" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 5</t>
-        </is>
-      </c>
-      <c r="AH6" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AI6" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AJ6" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AK6" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AL6" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="AM6" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AN6" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AO6" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E7" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F7" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I7" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J7" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K7" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="L7" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M7" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="N7" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="O7" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P7" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q7" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="R7" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S7" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="T7" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="U7" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="V7" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W7" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X7" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="Y7" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z7" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA7" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB7" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC7" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="AD7" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AE7" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="AF7" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 5</t>
-        </is>
-      </c>
-      <c r="AG7" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AH7" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AI7" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AJ7" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AK7" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AL7" s="41" t="inlineStr">
-        <is>
-          <t>WD B - 1</t>
-        </is>
-      </c>
-      <c r="AM7" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AN7" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="AO7" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E8" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F8" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H8" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I8" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J8" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K8" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="L8" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="N8" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="O8" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P8" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q8" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="R8" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S8" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="T8" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="U8" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="V8" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W8" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X8" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="Y8" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z8" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AA8" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AB8" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AC8" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="AD8" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AE8" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="AF8" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AG8" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AH8" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AI8" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AJ8" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AK8" s="44" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AL8" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="AM8" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AN8" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G9" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J9" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="L9" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M9" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="N9" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="O9" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P9" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q9" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="R9" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S9" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="T9" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="U9" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="V9" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W9" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="X9" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="Y9" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="Z9" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AA9" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AB9" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AC9" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="AD9" s="38" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AE9" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AF9" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AG9" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AH9" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AI9" s="38" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AJ9" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AK9" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="AL9" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="AM9" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 4</t>
-        </is>
-      </c>
-      <c r="AN9" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="I10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J10" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="L10" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="M10" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="N10" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="O10" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P10" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q10" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="R10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="T10" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="U10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="V10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W10" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="X10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="Y10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="Z10" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AA10" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="AB10" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AC10" s="36" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="AD10" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AE10" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AF10" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AG10" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AH10" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AI10" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AJ10" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AK10" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AL10" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="AN10" s="43" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="E11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="I11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="J11" s="32" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="K11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="L11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="M11" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="N11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="O11" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P11" s="33" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="Q11" s="30" t="inlineStr">
-        <is>
-          <t>MS C - 6</t>
-        </is>
-      </c>
-      <c r="R11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="T11" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="U11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="V11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W11" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="X11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="Y11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="Z11" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AA11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="AB11" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AC11" s="45" t="inlineStr">
-        <is>
-          <t>MD C - 5</t>
-        </is>
-      </c>
-      <c r="AD11" s="38" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AE11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AF11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AG11" s="40" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AH11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AI11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AJ11" s="42" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
-        </is>
-      </c>
-      <c r="AK11" s="46" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AL11" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="AN11" s="37" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
         </is>
       </c>
     </row>

--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -27395,2036 +27395,2036 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AR11"/>
+  <dimension ref="B2:AP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="47" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="C2" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="D2" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="E2" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="F2" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="G2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="H2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J2" s="47" t="inlineStr">
         <is>
           <t>MS C - 1</t>
         </is>
       </c>
-      <c r="C2" s="48" t="inlineStr">
+      <c r="K2" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="L2" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M2" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="N2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="O2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P2" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
+        </is>
+      </c>
+      <c r="Q2" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="R2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="S2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="T2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U2" s="48" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="V2" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W2" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+      <c r="X2" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Y2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Z2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AA2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB2" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AC2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AD2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AG2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AI2" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AJ2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="AK2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AM2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AN2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AO2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AP2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="C3" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="D3" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="E3" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="F3" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="G3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="H3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="L3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M3" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="N3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="O3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q3" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="R3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="S3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="T3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="V3" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W3" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="X3" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Y3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="Z3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AA3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB3" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AC3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AD3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AG3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AI3" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="AJ3" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 5</t>
+        </is>
+      </c>
+      <c r="AK3" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AM3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AO3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AP3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="D4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="E4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="G4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="L4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M4" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="N4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="O4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q4" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="R4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="S4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="V4" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="W4" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="X4" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Y4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="Z4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AA4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AC4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AD4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AG4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI4" s="49" t="inlineStr">
         <is>
           <t>XD V - 1</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="AJ4" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AK4" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AM4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AO4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="F5" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
         <is>
           <t>MS C - 2</t>
         </is>
       </c>
-      <c r="F2" s="50" t="inlineStr">
+      <c r="I5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+      <c r="L5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M5" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="N5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="O5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="R5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="S5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="V5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="W5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="X5" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Y5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="Z5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA5" s="50" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="G2" s="50" t="inlineStr">
+      <c r="AB5" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AC5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AD5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AG5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AJ5" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AK5" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="AM5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AO5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="G6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="H6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L6" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M6" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="N6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="O6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q6" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="R6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="S6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="V6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="W6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="Y6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="Z6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA6" s="50" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="AB6" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AC6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="AD6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH6" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI6" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ6" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AK6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AL6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="AM6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AO6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="G7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L7" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M7" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="O7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q7" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="R7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="S7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="V7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="W7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X7" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="Z7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB7" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AC7" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AD7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH7" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI7" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ7" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AK7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AL7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 5</t>
+        </is>
+      </c>
+      <c r="AM7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AO7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="E8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L8" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="M8" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="O8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q8" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="R8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 6</t>
+        </is>
+      </c>
+      <c r="S8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="V8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="W8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X8" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="Y8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="Z8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB8" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AC8" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AD8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH8" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AI8" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ8" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AK8" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AL8" s="51" t="inlineStr">
         <is>
           <t>MD V - 1</t>
         </is>
       </c>
-      <c r="I2" s="52" t="inlineStr">
+      <c r="AM8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN8" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AO8" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="C9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="D9" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="E9" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="G9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="H9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="M9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N9" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="O9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q9" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="R9" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="S9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="V9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="W9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X9" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="Y9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="Z9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB9" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AC9" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AD9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AE9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG9" s="52" t="inlineStr">
         <is>
           <t>MS A - 1</t>
         </is>
       </c>
-      <c r="J2" s="53" t="inlineStr">
+      <c r="AH9" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AI9" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ9" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AK9" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AL9" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AM9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN9" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AO9" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="D10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 5</t>
+        </is>
+      </c>
+      <c r="E10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 4</t>
+        </is>
+      </c>
+      <c r="G10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="M10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="N10" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="O10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q10" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="R10" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="S10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="V10" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 5</t>
+        </is>
+      </c>
+      <c r="W10" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X10" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="Y10" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Z10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB10" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="AC10" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AD10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AE10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH10" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+      <c r="AI10" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ10" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AK10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AL10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AM10" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AN10" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 5</t>
+        </is>
+      </c>
+      <c r="AO10" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 4</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="E11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="M11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="N11" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="O11" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="P11" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Q11" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="R11" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="S11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="T11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="U11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="V11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="W11" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="X11" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="Y11" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="Z11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AA11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AB11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AC11" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AD11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AE11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AF11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AG11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AH11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AI11" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AJ11" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AK11" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="AL11" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AM11" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AN11" s="53" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="K2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="L2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N2" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="O2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="Q2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="R2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="S2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="T2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="U2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="V2" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W2" s="55" t="inlineStr">
+      <c r="AO11" s="55" t="inlineStr">
         <is>
           <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="Y2" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AB2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AC2" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 4</t>
-        </is>
-      </c>
-      <c r="AD2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AE2" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AF2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AG2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AH2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 5</t>
-        </is>
-      </c>
-      <c r="AI2" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ2" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AK2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AM2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AO2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AP2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 5</t>
-        </is>
-      </c>
-      <c r="AQ2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 5</t>
-        </is>
-      </c>
-      <c r="AR2" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="D3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="E3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="G3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="I3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="K3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N3" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="O3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="R3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="S3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 5</t>
-        </is>
-      </c>
-      <c r="T3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 6</t>
-        </is>
-      </c>
-      <c r="U3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="V3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="Y3" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AB3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 5</t>
-        </is>
-      </c>
-      <c r="AD3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE3" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AF3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AG3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AH3" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ3" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK3" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AM3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AO3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AP3" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 4</t>
-        </is>
-      </c>
-      <c r="AQ3" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="D4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="E4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="G4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="K4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N4" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="O4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="R4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="V4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X4" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="Y4" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AB4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE4" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AF4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG4" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AH4" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ4" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK4" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AM4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN4" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="AO4" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AP4" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="AQ4" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="E5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="G5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="K5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="O5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="R5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="V5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X5" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="Y5" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AB5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE5" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AF5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG5" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AH5" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ5" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK5" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AM5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN5" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="AO5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 5</t>
-        </is>
-      </c>
-      <c r="AP5" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="AQ5" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="D6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="E6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="G6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="K6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="O6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="V6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X6" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="Y6" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA6" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AB6" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD6" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AF6" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="AH6" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI6" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ6" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK6" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL6" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AM6" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AN6" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="AO6" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="AQ6" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="E7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="K7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="O7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="V7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W7" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="X7" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="Y7" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA7" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AB7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD7" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AF7" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 5</t>
-        </is>
-      </c>
-      <c r="AH7" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI7" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ7" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK7" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL7" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AM7" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AN7" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="AO7" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="K8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="O8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="P8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="S8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="V8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="X8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="Y8" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="AB8" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AF8" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AH8" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AI8" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ8" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL8" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AM8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AN8" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="AO8" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D9" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 1</t>
-        </is>
-      </c>
-      <c r="E9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="K9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="L9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="O9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="P9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R9" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="S9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T9" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="V9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="W9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="X9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="Y9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Z9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="AB9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AC9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AF9" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AG9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AH9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
-        </is>
-      </c>
-      <c r="AI9" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
-        </is>
-      </c>
-      <c r="AJ9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AK9" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AM9" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AN9" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="AO9" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G10" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="H10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="J10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="K10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="L10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="O10" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="P10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R10" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="S10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="V10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="W10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="X10" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="Y10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="Z10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="AB10" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AC10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AF10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="AG10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AH10" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-      <c r="AI10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AJ10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 4</t>
-        </is>
-      </c>
-      <c r="AK10" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AL10" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AM10" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AO10" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="E11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="F11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="G11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="J11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="L11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="M11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 6</t>
-        </is>
-      </c>
-      <c r="N11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="O11" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="P11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="Q11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="R11" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="S11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="U11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="V11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="W11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="X11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 6</t>
-        </is>
-      </c>
-      <c r="Y11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="Z11" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="AA11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 5</t>
-        </is>
-      </c>
-      <c r="AB11" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AC11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AD11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AE11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="AF11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AG11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AI11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AL11" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="AM11" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AO11" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
         </is>
       </c>
     </row>

--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -27395,2036 +27395,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AP11"/>
+  <dimension ref="B2:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="C2" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="D2" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="E2" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F2" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="G2" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="H2" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I2" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J2" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K2" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="L2" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M2" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="N2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P2" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 4</t>
-        </is>
-      </c>
-      <c r="Q2" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="T2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V2" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W2" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 4</t>
-        </is>
-      </c>
-      <c r="X2" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Z2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB2" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AC2" s="52" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="H2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="J2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 5</t>
+        </is>
+      </c>
+      <c r="L2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="H3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="J3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 5</t>
+        </is>
+      </c>
+      <c r="L3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="H4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="J4" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 5</t>
+        </is>
+      </c>
+      <c r="L4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="H5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="J7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="H8" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="J8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="H9" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="J9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="H10" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="J10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="F11" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="H11" s="52" t="inlineStr">
         <is>
           <t>MS A - 4</t>
         </is>
       </c>
-      <c r="AD2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH2" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AI2" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AJ2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AK2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="AN2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="AO2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AP2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="C3" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="D3" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="E3" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F3" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="G3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="H3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="L3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M3" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="N3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q3" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="T3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X3" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB3" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AC3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AD3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AI3" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 4</t>
-        </is>
-      </c>
-      <c r="AJ3" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 5</t>
-        </is>
-      </c>
-      <c r="AK3" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="AO3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AP3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="C4" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="D4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F4" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="H4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="L4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M4" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="N4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q4" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X4" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB4" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="AD4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="AJ4" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK4" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C5" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="D5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F5" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 5</t>
-        </is>
-      </c>
-      <c r="L5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M5" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="N5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q5" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X5" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB5" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="AD5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="AJ5" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK5" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AM5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C6" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-      <c r="D6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F6" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M6" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-      <c r="N6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="O6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q6" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R6" s="48" t="inlineStr">
+      <c r="J11" s="48" t="inlineStr">
         <is>
           <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="S6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X6" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB6" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 6</t>
-        </is>
-      </c>
-      <c r="AD6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH6" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI6" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ6" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK6" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL6" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AM6" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C7" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F7" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="O7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q7" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="S7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X7" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="Z7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB7" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC7" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH7" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI7" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ7" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK7" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL7" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 5</t>
-        </is>
-      </c>
-      <c r="AM7" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN7" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO7" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="E8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F8" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="G8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M8" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
-        </is>
-      </c>
-      <c r="O8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q8" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 6</t>
-        </is>
-      </c>
-      <c r="S8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="W8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X8" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="Z8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB8" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AC8" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH8" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AI8" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ8" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 1</t>
-        </is>
-      </c>
-      <c r="AM8" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN8" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AO8" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="C9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D9" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="E9" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F9" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="G9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="H9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N9" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 1</t>
-        </is>
-      </c>
-      <c r="O9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="W9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X9" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 5</t>
-        </is>
-      </c>
-      <c r="Z9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB9" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AC9" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH9" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AI9" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ9" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK9" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL9" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM9" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN9" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AO9" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="C10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 5</t>
-        </is>
-      </c>
-      <c r="E10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F10" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 4</t>
-        </is>
-      </c>
-      <c r="G10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="H10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N10" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="O10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q10" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="R10" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V10" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 5</t>
-        </is>
-      </c>
-      <c r="W10" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X10" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="Y10" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Z10" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA10" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB10" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
-        </is>
-      </c>
-      <c r="AC10" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AE10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH10" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 5</t>
-        </is>
-      </c>
-      <c r="AI10" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ10" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK10" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL10" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM10" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN10" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 5</t>
-        </is>
-      </c>
-      <c r="AO10" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 4</t>
-        </is>
-      </c>
-      <c r="C11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D11" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="E11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="G11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 6</t>
-        </is>
-      </c>
-      <c r="H11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="K11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="N11" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="O11" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P11" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q11" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="R11" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="W11" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X11" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="Y11" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Z11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AC11" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AE11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AI11" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ11" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AK11" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AL11" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM11" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN11" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="AO11" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
         </is>
       </c>
     </row>

--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -27399,2032 +27399,2032 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="D2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="H2" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="M2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="N2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="O2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P2" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="Q2" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="R2" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="S2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="U2" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="W2" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X2" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Y2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z2" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA2" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC2" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AD2" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AE2" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AF2" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AG2" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AH2" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AI2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AK2" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AL2" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="AM2" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="AN2" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AO2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AP2" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="F3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="H3" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="M3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="N3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="O3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P3" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="Q3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="R3" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="S3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="U3" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V3" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="W3" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X3" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Y3" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z3" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC3" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AD3" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AE3" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AF3" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AG3" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH3" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AI3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AK3" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AL3" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AM3" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="AN3" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="AO3" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="AP3" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L4" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="M4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="N4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="O4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="Q4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="R4" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="S4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="U4" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V4" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="W4" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Y4" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z4" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB4" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC4" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AD4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE4" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AF4" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AG4" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH4" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AI4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ4" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="AK4" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+      <c r="AL4" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AM4" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="AN4" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+      <c r="AO4" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="N5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="O5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P5" s="65" t="inlineStr">
         <is>
           <t>XD C - 1</t>
         </is>
       </c>
-      <c r="C2" s="66" t="inlineStr">
+      <c r="Q5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="R5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="S5" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="U5" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W5" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X5" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z5" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB5" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AD5" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AF5" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AG5" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH5" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AI5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ5" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="AK5" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="AL5" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
+        </is>
+      </c>
+      <c r="AM5" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="AN5" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AO5" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G6" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="H6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="N6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="O6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P6" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="Q6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="R6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="S6" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="U6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V6" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X6" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB6" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC6" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AD6" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AE6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF6" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AG6" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH6" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI6" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ6" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AK6" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="AL6" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AM6" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+      <c r="AN6" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AO6" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="N7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="O7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="P7" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="Q7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="R7" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S7" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="U7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V7" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W7" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="X7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="Z7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AA7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB7" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC7" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AD7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="AE7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AG7" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AH7" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI7" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="AJ7" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AK7" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+      <c r="AL7" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AM7" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="AN7" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="AO7" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J8" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="K8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="N8" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="P8" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="Q8" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="R8" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="T8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="U8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V8" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="X8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y8" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z8" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA8" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB8" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC8" s="66" t="inlineStr">
         <is>
           <t>WD C - 1</t>
         </is>
       </c>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="AD8" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="AE8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF8" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AG8" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AH8" s="49" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="AI8" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AJ8" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="AK8" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AL8" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="AM8" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="AN8" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AO8" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="H9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="J9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="K9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M9" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="N9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="P9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="Q9" s="64" t="inlineStr">
         <is>
           <t>MD C - 2</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
+      <c r="R9" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="T9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="U9" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="V9" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="X9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y9" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z9" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA9" s="53" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AB9" s="55" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC9" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="AD9" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="AE9" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AF9" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AG9" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AH9" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AI9" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AJ9" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AK9" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AL9" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AM9" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 5</t>
+        </is>
+      </c>
+      <c r="AN9" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AO9" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="F10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="J10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="K10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L10" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M10" s="64" t="inlineStr">
         <is>
           <t>MD C - 1</t>
         </is>
       </c>
-      <c r="F2" s="60" t="inlineStr">
+      <c r="N10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="P10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="Q10" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="R10" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S10" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="T10" s="60" t="inlineStr">
         <is>
           <t>WS C - 1</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="U10" s="47" t="inlineStr">
         <is>
           <t>MS C - 3</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
+      <c r="V10" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="X10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y10" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z10" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AB10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AC10" s="66" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="AD10" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="AE10" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AF10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AG10" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AH10" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AI10" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AJ10" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AK10" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 4</t>
+        </is>
+      </c>
+      <c r="AL10" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AM10" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="AN10" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="AO10" s="54" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>MS C - 2</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="F11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>MS C - 2</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K2" s="59" t="inlineStr">
+      <c r="H11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="J11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="K11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="L11" s="58" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="N11" s="59" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="O11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="P11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="Q11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="R11" s="59" t="inlineStr">
         <is>
           <t>XD B - 3</t>
         </is>
       </c>
-      <c r="L2" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M2" s="61" t="inlineStr">
+      <c r="S11" s="56" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="T11" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="U11" s="47" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="V11" s="63" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="W11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="X11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="Y11" s="57" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="Z11" s="52" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AA11" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="AB11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AC11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AD11" s="60" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="AE11" s="61" t="inlineStr">
         <is>
           <t>WD B - 2</t>
         </is>
       </c>
-      <c r="N2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O2" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P2" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 4</t>
-        </is>
-      </c>
-      <c r="Q2" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R2" s="48" t="inlineStr">
+      <c r="AF11" s="48" t="inlineStr">
         <is>
           <t>MS B - 4</t>
         </is>
       </c>
-      <c r="S2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="T2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U2" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V2" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W2" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 4</t>
-        </is>
-      </c>
-      <c r="X2" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Z2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA2" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB2" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AC2" s="52" t="inlineStr">
+      <c r="AG11" s="62" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="AH11" s="52" t="inlineStr">
         <is>
           <t>MS A - 4</t>
         </is>
       </c>
-      <c r="AD2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG2" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH2" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AI2" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AJ2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AK2" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM2" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="AN2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="AO2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AP2" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="C3" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="D3" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="E3" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F3" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="G3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="H3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J3" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="L3" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M3" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="N3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="P3" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q3" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="T3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U3" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="W3" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X3" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA3" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB3" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AC3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AD3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG3" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH3" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AI3" s="54" t="inlineStr">
+      <c r="AI11" s="51" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AJ11" s="65" t="inlineStr">
+        <is>
+          <t>XD C - 4</t>
+        </is>
+      </c>
+      <c r="AK11" s="64" t="inlineStr">
+        <is>
+          <t>MD C - 5</t>
+        </is>
+      </c>
+      <c r="AL11" s="61" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="AM11" s="48" t="inlineStr">
+        <is>
+          <t>MS B - 6</t>
+        </is>
+      </c>
+      <c r="AN11" s="50" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="AO11" s="54" t="inlineStr">
         <is>
           <t>WD V - 4</t>
-        </is>
-      </c>
-      <c r="AJ3" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 5</t>
-        </is>
-      </c>
-      <c r="AK3" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM3" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="AO3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AP3" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="C4" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="D4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E4" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F4" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="H4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J4" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="L4" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M4" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="N4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P4" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q4" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U4" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W4" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X4" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AA4" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB4" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="AD4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG4" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI4" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="AJ4" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK4" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AM4" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO4" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C5" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="D5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="F5" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J5" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 5</t>
-        </is>
-      </c>
-      <c r="L5" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M5" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="N5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="O5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P5" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q5" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="R5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="S5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U5" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W5" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="X5" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Y5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA5" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB5" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="AD5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AG5" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI5" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="AJ5" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK5" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AM5" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO5" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C6" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-      <c r="D6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E6" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F6" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="I6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K6" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L6" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M6" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-      <c r="N6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="O6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P6" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q6" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="S6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U6" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W6" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X6" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="Z6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA6" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB6" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 6</t>
-        </is>
-      </c>
-      <c r="AD6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG6" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH6" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI6" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ6" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AK6" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AL6" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="AM6" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO6" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C7" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="E7" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F7" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="G7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K7" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M7" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="O7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P7" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q7" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="S7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U7" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="V7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="W7" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X7" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="Z7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA7" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB7" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AC7" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG7" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH7" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AI7" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ7" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK7" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL7" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 5</t>
-        </is>
-      </c>
-      <c r="AM7" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN7" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AO7" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="C8" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="E8" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F8" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="G8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="H8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K8" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L8" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="M8" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
-        </is>
-      </c>
-      <c r="O8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P8" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q8" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 6</t>
-        </is>
-      </c>
-      <c r="S8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U8" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="W8" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X8" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="Z8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA8" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB8" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AC8" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG8" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH8" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AI8" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ8" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL8" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 1</t>
-        </is>
-      </c>
-      <c r="AM8" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN8" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AO8" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="C9" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D9" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="E9" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F9" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="G9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="H9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K9" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M9" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N9" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 1</t>
-        </is>
-      </c>
-      <c r="O9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P9" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="R9" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U9" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="W9" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X9" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="Y9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 5</t>
-        </is>
-      </c>
-      <c r="Z9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA9" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB9" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AC9" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="AE9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG9" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH9" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="AI9" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ9" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK9" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL9" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM9" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN9" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AO9" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="C10" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 5</t>
-        </is>
-      </c>
-      <c r="E10" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F10" s="60" t="inlineStr">
-        <is>
-          <t>WS C - 4</t>
-        </is>
-      </c>
-      <c r="G10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="H10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="K10" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 1</t>
-        </is>
-      </c>
-      <c r="N10" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="O10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P10" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q10" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="R10" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U10" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V10" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 5</t>
-        </is>
-      </c>
-      <c r="W10" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X10" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="Y10" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Z10" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA10" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB10" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
-        </is>
-      </c>
-      <c r="AC10" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AE10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG10" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH10" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 5</t>
-        </is>
-      </c>
-      <c r="AI10" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ10" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AK10" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="AL10" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM10" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AN10" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 5</t>
-        </is>
-      </c>
-      <c r="AO10" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 4</t>
-        </is>
-      </c>
-      <c r="C11" s="65" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="D11" s="66" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="E11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="F11" s="64" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="G11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 6</t>
-        </is>
-      </c>
-      <c r="H11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="I11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="J11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="K11" s="47" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="L11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="M11" s="59" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="N11" s="61" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="O11" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="P11" s="58" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="Q11" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 3</t>
-        </is>
-      </c>
-      <c r="R11" s="63" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="S11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="T11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="U11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="V11" s="48" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="W11" s="56" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="X11" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="Y11" s="62" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="Z11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="AA11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AB11" s="50" t="inlineStr">
-        <is>
-          <t>MD A - 1</t>
-        </is>
-      </c>
-      <c r="AC11" s="57" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="AD11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="AE11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AF11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="AG11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AH11" s="52" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AI11" s="49" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AJ11" s="54" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AK11" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="AL11" s="51" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AM11" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 3</t>
-        </is>
-      </c>
-      <c r="AN11" s="53" t="inlineStr">
-        <is>
-          <t>WS V - 1</t>
-        </is>
-      </c>
-      <c r="AO11" s="55" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
         </is>
       </c>
     </row>

--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sofienystrom/Badminton-Timetable-Solver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A168F64B-0213-A64A-80E6-1F4A6F866835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E02814-FDC4-CD48-AF21-2F15B1E459EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16680" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries HBC Premier Elite 2024" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="Player Events" sheetId="3" r:id="rId3"/>
     <sheet name="Rule Violations" sheetId="4" r:id="rId4"/>
     <sheet name="Event Analysis" sheetId="5" r:id="rId5"/>
-    <sheet name="timetable" sheetId="6" r:id="rId6"/>
+    <sheet name="timetable-12 40" sheetId="6" r:id="rId6"/>
+    <sheet name="timetable" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="1175">
   <si>
     <t>Entries of MS V - Main Draw</t>
   </si>
@@ -3270,286 +3271,286 @@
     <t>WD C (8), WS C (5), WD B (3), WS B (3), MS C (9), MD C (8), MD B (2)</t>
   </si>
   <si>
+    <t>WD B - 1</t>
+  </si>
+  <si>
     <t>MS C - 1</t>
   </si>
   <si>
+    <t>MS C - 2</t>
+  </si>
+  <si>
+    <t>MS B - 1</t>
+  </si>
+  <si>
+    <t>MS B - 2</t>
+  </si>
+  <si>
+    <t>WD V - 1</t>
+  </si>
+  <si>
+    <t>XD A - 1</t>
+  </si>
+  <si>
+    <t>XD B - 1</t>
+  </si>
+  <si>
+    <t>MS V - 1</t>
+  </si>
+  <si>
     <t>MS A - 1</t>
   </si>
   <si>
-    <t>MS B - 1</t>
-  </si>
-  <si>
-    <t>MS C - 2</t>
-  </si>
-  <si>
-    <t>XD A - 1</t>
-  </si>
-  <si>
-    <t>MS B - 2</t>
+    <t>XD V - 1</t>
+  </si>
+  <si>
+    <t>XD A - 2</t>
+  </si>
+  <si>
+    <t>WS V - 1</t>
+  </si>
+  <si>
+    <t>XD A - 3</t>
   </si>
   <si>
     <t>MS A - 2</t>
   </si>
   <si>
+    <t>XD B - 3</t>
+  </si>
+  <si>
+    <t>MS A - 3</t>
+  </si>
+  <si>
+    <t>MD V - 1</t>
+  </si>
+  <si>
     <t>MD A - 1</t>
   </si>
   <si>
+    <t>MD V - 2</t>
+  </si>
+  <si>
+    <t>MD A - 2</t>
+  </si>
+  <si>
+    <t>XD V - 2</t>
+  </si>
+  <si>
+    <t>MD A - 3</t>
+  </si>
+  <si>
+    <t>XD V - 3</t>
+  </si>
+  <si>
+    <t>XD A - 4</t>
+  </si>
+  <si>
+    <t>MD A - 4</t>
+  </si>
+  <si>
+    <t>XD V - 4</t>
+  </si>
+  <si>
+    <t>XD B - 5</t>
+  </si>
+  <si>
+    <t>XD V - 5</t>
+  </si>
+  <si>
+    <t>WD V - 3</t>
+  </si>
+  <si>
+    <t>WD A - 3</t>
+  </si>
+  <si>
+    <t>MD V - 3</t>
+  </si>
+  <si>
+    <t>XD C - 2</t>
+  </si>
+  <si>
+    <t>MD V - 4</t>
+  </si>
+  <si>
+    <t>MS C - 3</t>
+  </si>
+  <si>
+    <t>WS V - 2</t>
+  </si>
+  <si>
+    <t>MD B - 4</t>
+  </si>
+  <si>
+    <t>MS V - 2</t>
+  </si>
+  <si>
+    <t>WS A - 1</t>
+  </si>
+  <si>
+    <t>MS B - 3</t>
+  </si>
+  <si>
+    <t>MS V - 3</t>
+  </si>
+  <si>
+    <t>WS A - 2</t>
+  </si>
+  <si>
+    <t>MS B - 5</t>
+  </si>
+  <si>
+    <t>MS V - 4</t>
+  </si>
+  <si>
+    <t>MS B - 6</t>
+  </si>
+  <si>
+    <t>MS V - 5</t>
+  </si>
+  <si>
+    <t>MD C - 1</t>
+  </si>
+  <si>
     <t>MD B - 1</t>
   </si>
   <si>
-    <t>MS V - 1</t>
-  </si>
-  <si>
-    <t>XD A - 2</t>
-  </si>
-  <si>
-    <t>MS V - 2</t>
-  </si>
-  <si>
-    <t>XD A - 3</t>
-  </si>
-  <si>
-    <t>XD V - 2</t>
-  </si>
-  <si>
-    <t>WS V - 1</t>
-  </si>
-  <si>
-    <t>MD A - 2</t>
-  </si>
-  <si>
-    <t>WS V - 2</t>
-  </si>
-  <si>
-    <t>MD V - 2</t>
-  </si>
-  <si>
-    <t>MS A - 3</t>
-  </si>
-  <si>
-    <t>WS A - 1</t>
+    <t>WD V - 2</t>
+  </si>
+  <si>
+    <t>XD A - 5</t>
+  </si>
+  <si>
+    <t>MD A - 5</t>
+  </si>
+  <si>
+    <t>WS B - 4</t>
+  </si>
+  <si>
+    <t>WS V - 5</t>
+  </si>
+  <si>
+    <t>XD B - 2</t>
+  </si>
+  <si>
+    <t>WD A - 1</t>
+  </si>
+  <si>
+    <t>WD A - 2</t>
+  </si>
+  <si>
+    <t>WD B - 2</t>
+  </si>
+  <si>
+    <t>WS C - 1</t>
+  </si>
+  <si>
+    <t>WD A - 4</t>
+  </si>
+  <si>
+    <t>WD C - 2</t>
+  </si>
+  <si>
+    <t>WD C - 3</t>
+  </si>
+  <si>
+    <t>MD B - 5</t>
+  </si>
+  <si>
+    <t>WS V - 3</t>
+  </si>
+  <si>
+    <t>WS B - 3</t>
+  </si>
+  <si>
+    <t>WS V - 4</t>
+  </si>
+  <si>
+    <t>MS A - 6</t>
+  </si>
+  <si>
+    <t>XD C - 1</t>
+  </si>
+  <si>
+    <t>MD B - 2</t>
+  </si>
+  <si>
+    <t>MD B - 3</t>
+  </si>
+  <si>
+    <t>WS C - 2</t>
+  </si>
+  <si>
+    <t>XD C - 3</t>
+  </si>
+  <si>
+    <t>WS A - 4</t>
+  </si>
+  <si>
+    <t>MD C - 3</t>
+  </si>
+  <si>
+    <t>MD C - 4</t>
+  </si>
+  <si>
+    <t>WD V - 4</t>
+  </si>
+  <si>
+    <t>MD V - 5</t>
+  </si>
+  <si>
+    <t>MS B - 4</t>
+  </si>
+  <si>
+    <t>MS A - 5</t>
+  </si>
+  <si>
+    <t>XD C - 4</t>
+  </si>
+  <si>
+    <t>WD C - 1</t>
+  </si>
+  <si>
+    <t>XD B - 4</t>
+  </si>
+  <si>
+    <t>WS B - 1</t>
+  </si>
+  <si>
+    <t>WD B - 3</t>
   </si>
   <si>
     <t>MS A - 4</t>
   </si>
   <si>
-    <t>WS V - 3</t>
-  </si>
-  <si>
-    <t>MD V - 3</t>
-  </si>
-  <si>
-    <t>XD V - 4</t>
-  </si>
-  <si>
-    <t>MD V - 4</t>
-  </si>
-  <si>
-    <t>WD V - 2</t>
-  </si>
-  <si>
-    <t>MS V - 3</t>
-  </si>
-  <si>
-    <t>WD V - 3</t>
-  </si>
-  <si>
-    <t>MS V - 4</t>
-  </si>
-  <si>
-    <t>MS A - 5</t>
-  </si>
-  <si>
-    <t>MS V - 5</t>
-  </si>
-  <si>
-    <t>MD V - 5</t>
-  </si>
-  <si>
-    <t>WS V - 5</t>
-  </si>
-  <si>
-    <t>XD B - 2</t>
+    <t>MD C - 2</t>
   </si>
   <si>
     <t>WS A - 3</t>
   </si>
   <si>
-    <t>WS V - 4</t>
-  </si>
-  <si>
-    <t>WD V - 4</t>
-  </si>
-  <si>
-    <t>MS A - 6</t>
-  </si>
-  <si>
-    <t>MD B - 2</t>
-  </si>
-  <si>
-    <t>MD V - 1</t>
-  </si>
-  <si>
-    <t>WD A - 1</t>
-  </si>
-  <si>
-    <t>XD V - 3</t>
-  </si>
-  <si>
-    <t>WD V - 1</t>
-  </si>
-  <si>
-    <t>WD B - 2</t>
-  </si>
-  <si>
-    <t>MD B - 3</t>
+    <t>MS C - 4</t>
   </si>
   <si>
     <t>WD B - 4</t>
   </si>
   <si>
-    <t>MS B - 5</t>
-  </si>
-  <si>
-    <t>XD V - 5</t>
-  </si>
-  <si>
-    <t>MS B - 3</t>
-  </si>
-  <si>
-    <t>WS B - 1</t>
-  </si>
-  <si>
-    <t>WS A - 2</t>
-  </si>
-  <si>
-    <t>WD B - 3</t>
-  </si>
-  <si>
-    <t>XD B - 4</t>
-  </si>
-  <si>
-    <t>MD A - 4</t>
-  </si>
-  <si>
-    <t>WS A - 4</t>
-  </si>
-  <si>
-    <t>MS C - 3</t>
-  </si>
-  <si>
-    <t>XD B - 1</t>
-  </si>
-  <si>
-    <t>XD V - 1</t>
-  </si>
-  <si>
-    <t>MS B - 4</t>
-  </si>
-  <si>
-    <t>XD B - 3</t>
-  </si>
-  <si>
-    <t>WS B - 3</t>
-  </si>
-  <si>
-    <t>MS B - 6</t>
-  </si>
-  <si>
-    <t>MD A - 5</t>
-  </si>
-  <si>
-    <t>MS C - 4</t>
+    <t>WS B - 2</t>
+  </si>
+  <si>
+    <t>MS C - 6</t>
   </si>
   <si>
     <t>WS C - 3</t>
   </si>
   <si>
-    <t>WD A - 3</t>
-  </si>
-  <si>
-    <t>WS B - 4</t>
-  </si>
-  <si>
-    <t>WD A - 4</t>
-  </si>
-  <si>
-    <t>MD C - 2</t>
-  </si>
-  <si>
-    <t>XD C - 1</t>
-  </si>
-  <si>
-    <t>XD C - 2</t>
-  </si>
-  <si>
-    <t>WD A - 2</t>
-  </si>
-  <si>
-    <t>MD A - 3</t>
-  </si>
-  <si>
-    <t>WS C - 1</t>
-  </si>
-  <si>
-    <t>WS C - 2</t>
-  </si>
-  <si>
-    <t>MD B - 4</t>
-  </si>
-  <si>
-    <t>MD B - 5</t>
-  </si>
-  <si>
-    <t>XD A - 5</t>
-  </si>
-  <si>
-    <t>MD C - 1</t>
-  </si>
-  <si>
-    <t>MD C - 3</t>
+    <t>WS C - 4</t>
   </si>
   <si>
     <t>MS C - 5</t>
   </si>
   <si>
-    <t>WD C - 1</t>
-  </si>
-  <si>
-    <t>MD C - 4</t>
-  </si>
-  <si>
-    <t>XD A - 4</t>
-  </si>
-  <si>
-    <t>WS C - 4</t>
-  </si>
-  <si>
-    <t>XD B - 5</t>
-  </si>
-  <si>
-    <t>WS B - 2</t>
-  </si>
-  <si>
-    <t>XD C - 3</t>
-  </si>
-  <si>
     <t>MD C - 5</t>
-  </si>
-  <si>
-    <t>MS C - 6</t>
-  </si>
-  <si>
-    <t>WD B - 1</t>
-  </si>
-  <si>
-    <t>WD C - 2</t>
-  </si>
-  <si>
-    <t>XD C - 4</t>
-  </si>
-  <si>
-    <t>WD C - 3</t>
   </si>
 </sst>
 </file>
@@ -3610,8 +3611,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
-        <bgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FF64B5F6"/>
+        <bgColor rgb="FF64B5F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -3628,8 +3629,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66BB6A"/>
-        <bgColor rgb="FF66BB6A"/>
+        <fgColor rgb="FFBBDEFB"/>
+        <bgColor rgb="FFBBDEFB"/>
       </patternFill>
     </fill>
     <fill>
@@ -3640,8 +3641,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF48FB1"/>
-        <bgColor rgb="FFF48FB1"/>
+        <fgColor rgb="FF42A5F5"/>
+        <bgColor rgb="FF42A5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90CAF9"/>
+        <bgColor rgb="FF90CAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66BB6A"/>
+        <bgColor rgb="FF66BB6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCA28"/>
+        <bgColor rgb="FFFFCA28"/>
       </patternFill>
     </fill>
     <fill>
@@ -3652,32 +3671,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE082"/>
-        <bgColor rgb="FFFFE082"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEC407A"/>
         <bgColor rgb="FFEC407A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42A5F5"/>
-        <bgColor rgb="FF42A5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBDEFB"/>
-        <bgColor rgb="FFBBDEFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90CAF9"/>
-        <bgColor rgb="FF90CAF9"/>
       </patternFill>
     </fill>
     <fill>
@@ -3688,14 +3683,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCA28"/>
-        <bgColor rgb="FFFFCA28"/>
+        <fgColor rgb="FFFFF8E1"/>
+        <bgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8E6C9"/>
-        <bgColor rgb="FFC8E6C9"/>
+        <fgColor rgb="FF81C784"/>
+        <bgColor rgb="FF81C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE082"/>
+        <bgColor rgb="FFFFE082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD54F"/>
+        <bgColor rgb="FFFFD54F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFECB3"/>
+        <bgColor rgb="FFFFECB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -3706,26 +3719,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF81C784"/>
-        <bgColor rgb="FF81C784"/>
+        <fgColor rgb="FFF48FB1"/>
+        <bgColor rgb="FFF48FB1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF64B5F6"/>
-        <bgColor rgb="FF64B5F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFECB3"/>
-        <bgColor rgb="FFFFECB3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD54F"/>
-        <bgColor rgb="FFFFD54F"/>
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -3785,19 +3786,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18965,8 +18966,8 @@
     <col min="1" max="1" width="29.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="8.83203125" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="7"/>
+    <col min="4" max="11" width="8.83203125" style="7" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -22860,1233 +22861,2477 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B2:AP11"/>
+  <dimension ref="B2:BB13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:54" x14ac:dyDescent="0.2">
       <c r="B2" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T2" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z2" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB2" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AE2" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF2" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG2" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI2" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AK2" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AL2" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM2" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN2" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO2" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP2" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ2" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AR2" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AS2" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AT2" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU2" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AV2" s="27" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AW2" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AX2" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AY2" s="21" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AZ2" s="15" t="s">
+        <v>1125</v>
+      </c>
+      <c r="BA2" s="18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="BB2" s="22" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="3" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C3" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U3" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Y3" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z3" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA3" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC3" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE3" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF3" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG3" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AK3" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AL3" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM3" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN3" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO3" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP3" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AS3" s="24" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AT3" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU3" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AV3" s="28" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AW3" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AX3" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AY3" s="16" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
+        <v>1132</v>
+      </c>
+      <c r="BA3" s="20" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="4" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C4" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T4" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X4" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y4" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA4" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC4" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD4" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF4" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG4" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH4" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI4" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ4" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AK4" s="24" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AL4" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM4" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN4" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO4" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AP4" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ4" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AS4" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AT4" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AU4" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AW4" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AX4" s="25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AY4" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="BA4" s="30" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="5" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C5" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="S5" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U5" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V5" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y5" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z5" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA5" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB5" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD5" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE5" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF5" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG5" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH5" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI5" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ5" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AK5" s="24" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AL5" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM5" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN5" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO5" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AP5" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AS5" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AT5" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AU5" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AW5" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AX5" s="25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AY5" s="26" t="s">
+        <v>1152</v>
+      </c>
+      <c r="BA5" s="31" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="6" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C6" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U6" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X6" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y6" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z6" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC6" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD6" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE6" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF6" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG6" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH6" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI6" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ6" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AM6" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN6" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO6" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ6" s="13" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AS6" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AU6" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AW6" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AY6" s="23" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="7" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D7" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U7" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V7" s="28" t="s">
         <v>1081</v>
       </c>
+      <c r="W7" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X7" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y7" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB7" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC7" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD7" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF7" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG7" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH7" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI7" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ7" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AK7" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AM7" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN7" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO7" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP7" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS7" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AU7" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW7" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AY7" s="30" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="8" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D8" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U8" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V8" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X8" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y8" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z8" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB8" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC8" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF8" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG8" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH8" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI8" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ8" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM8" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN8" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO8" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP8" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS8" s="32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AU8" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW8" s="26" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AY8" s="30" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="9" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D9" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U9" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V9" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X9" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y9" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z9" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB9" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD9" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF9" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG9" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH9" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ9" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM9" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN9" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO9" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP9" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ9" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS9" s="32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AU9" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW9" s="26" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="10" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D10" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="V10" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X10" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y10" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z10" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB10" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC10" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD10" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF10" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH10" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ10" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM10" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN10" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO10" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP10" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ10" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AU10" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW10" s="23" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="11" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D11" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q11" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="W11" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X11" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AC11" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD11" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE11" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF11" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH11" s="30" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AI11" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ11" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM11" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN11" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO11" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP11" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ11" s="31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AU11" s="29" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AW11" s="23" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="12" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D12" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="W12" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X12" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y12" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AC12" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD12" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE12" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF12" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH12" s="30" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AJ12" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM12" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN12" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO12" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP12" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ12" s="31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AW12" s="32" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="13" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D13" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="W13" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X13" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y13" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AC13" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD13" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE13" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF13" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AJ13" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM13" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN13" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO13" s="23" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B2:BB13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="B2" s="13" t="s">
+        <v>1086</v>
+      </c>
       <c r="C2" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T2" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W2" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="X2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z2" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB2" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD2" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AE2" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF2" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG2" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI2" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AK2" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AL2" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM2" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN2" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO2" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP2" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ2" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AR2" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AS2" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AT2" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU2" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AV2" s="27" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AW2" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AX2" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AY2" s="21" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AZ2" s="15" t="s">
+        <v>1125</v>
+      </c>
+      <c r="BA2" s="18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="BB2" s="22" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="3" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C3" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U3" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W3" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="X3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Y3" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z3" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA3" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC3" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE3" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF3" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG3" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AK3" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AL3" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM3" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN3" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO3" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP3" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AS3" s="24" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AT3" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU3" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AV3" s="28" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AW3" s="21" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AX3" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AY3" s="16" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
+        <v>1132</v>
+      </c>
+      <c r="BA3" s="20" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="4" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C4" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T4" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X4" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y4" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA4" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC4" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD4" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF4" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG4" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH4" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI4" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ4" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AK4" s="24" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AL4" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM4" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN4" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO4" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AP4" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ4" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AS4" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AT4" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AU4" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AW4" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AX4" s="25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AY4" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="BA4" s="30" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="5" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C5" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="S5" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U5" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V5" s="21" t="s">
+        <v>1118</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y5" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z5" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA5" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AB5" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD5" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE5" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF5" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AG5" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH5" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI5" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ5" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AK5" s="24" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AL5" s="22" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AM5" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN5" s="25" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AO5" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AP5" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AS5" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AT5" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AU5" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AW5" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AX5" s="25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AY5" s="26" t="s">
+        <v>1152</v>
+      </c>
+      <c r="BA5" s="31" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="6" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="C6" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U6" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X6" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y6" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z6" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AC6" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD6" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AE6" s="23" t="s">
         <v>1083</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="AF6" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG6" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH6" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AI6" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ6" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AM6" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN6" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO6" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ6" s="13" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AS6" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AU6" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AW6" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AY6" s="23" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="7" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D7" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>1084</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G7" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>1085</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N2" s="19" t="s">
+      <c r="J7" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U7" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="V7" s="28" t="s">
+        <v>1081</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X7" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Y7" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB7" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC7" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD7" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF7" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG7" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH7" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI7" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ7" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AK7" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AM7" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN7" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO7" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP7" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS7" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AU7" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW7" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AY7" s="30" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="8" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D8" s="14" t="s">
         <v>1090</v>
       </c>
-      <c r="O2" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="P2" s="19" t="s">
+      <c r="E8" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U8" s="20" t="s">
         <v>1092</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="V8" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X8" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y8" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z8" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB8" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC8" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF8" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG8" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH8" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI8" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AJ8" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM8" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN8" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO8" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP8" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS8" s="32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AU8" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW8" s="26" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AY8" s="30" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="9" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D9" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U9" s="20" t="s">
         <v>1092</v>
       </c>
-      <c r="R2" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="S2" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U2" s="21" t="s">
+      <c r="V9" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X9" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y9" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="V2" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W2" s="21" t="s">
+      <c r="Z9" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB9" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC9" s="14" t="s">
         <v>1097</v>
       </c>
-      <c r="X2" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y2" s="14" t="s">
+      <c r="AD9" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF9" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AG9" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AH9" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ9" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM9" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AN9" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO9" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP9" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ9" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AS9" s="32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AU9" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW9" s="26" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="10" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D10" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>1099</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="J10" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>1113</v>
+      </c>
+      <c r="V10" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X10" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y10" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Z10" s="31" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AB10" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AC10" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD10" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF10" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH10" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ10" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM10" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN10" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO10" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP10" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ10" s="14" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AU10" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW10" s="23" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="11" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D11" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G11" s="17" t="s">
         <v>1099</v>
       </c>
-      <c r="AA2" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AD2" s="21" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AE2" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AF2" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AG2" s="20" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AH2" s="22" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AI2" s="24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AJ2" s="19" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AK2" s="24" t="s">
-        <v>1108</v>
-      </c>
-      <c r="AL2" s="19" t="s">
-        <v>1109</v>
-      </c>
-      <c r="AM2" s="14" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AN2" s="19" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AO2" s="22" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AP2" s="21" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="3" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B3" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="J11" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q11" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="W11" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="X11" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AC11" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD11" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE11" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF11" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH11" s="30" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AI11" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AJ11" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM11" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN11" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO11" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP11" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ11" s="31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AU11" s="29" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AW11" s="23" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="12" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D12" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="W12" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="X12" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y12" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AC12" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD12" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE12" s="23" t="s">
         <v>1083</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="AF12" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AH12" s="30" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AJ12" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM12" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN12" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO12" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP12" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AQ12" s="31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AW12" s="32" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="13" spans="2:54" x14ac:dyDescent="0.2">
+      <c r="D13" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>1085</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="S3" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="T3" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U3" s="21" t="s">
+      <c r="W13" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X13" s="24" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Y13" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="V3" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X3" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y3" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Z3" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="AA3" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB3" s="14" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AC3" s="14" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AE3" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AF3" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AG3" s="20" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AH3" s="22" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AI3" s="24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AJ3" s="19" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AK3" s="24" t="s">
-        <v>1108</v>
-      </c>
-      <c r="AL3" s="19" t="s">
-        <v>1109</v>
-      </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AC13" s="31" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AD13" s="32" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE13" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AF13" s="23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AJ13" s="27" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AM13" s="31" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AN13" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AO13" s="23" t="s">
         <v>1115</v>
-      </c>
-      <c r="AN3" s="21" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AO3" s="24" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AP3" s="14" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="4" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B4" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N4" s="19" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R4" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T4" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U4" s="22" t="s">
-        <v>1120</v>
-      </c>
-      <c r="V4" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W4" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X4" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y4" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Z4" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB4" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AD4" s="21" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AE4" s="20" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AF4" s="24" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AG4" s="27" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AH4" s="24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AI4" s="18" t="s">
-        <v>1125</v>
-      </c>
-      <c r="AJ4" s="19" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AK4" s="27" t="s">
-        <v>1126</v>
-      </c>
-      <c r="AL4" s="15" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AM4" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AN4" s="21" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AO4" s="20" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="5" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B5" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R5" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T5" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V5" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W5" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X5" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y5" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Z5" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA5" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB5" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC5" s="23" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AD5" s="23" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AE5" s="20" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AF5" s="24" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AG5" s="27" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AH5" s="24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AI5" s="27" t="s">
-        <v>1132</v>
-      </c>
-      <c r="AJ5" s="19" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AK5" s="25" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AL5" s="15" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AM5" s="17" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AN5" s="14" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AO5" s="23" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="6" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>1137</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>1138</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R6" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="S6" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T6" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U6" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V6" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W6" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X6" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y6" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Z6" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA6" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB6" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC6" s="15" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AD6" s="23" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AE6" s="20" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AF6" s="24" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AG6" s="27" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AH6" s="25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AI6" s="27" t="s">
-        <v>1132</v>
-      </c>
-      <c r="AJ6" s="18" t="s">
-        <v>1125</v>
-      </c>
-      <c r="AK6" s="25" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AL6" s="28" t="s">
-        <v>1141</v>
-      </c>
-      <c r="AM6" s="17" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AN6" s="15" t="s">
-        <v>1142</v>
-      </c>
-      <c r="AO6" s="17" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="7" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>1090</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>1137</v>
-      </c>
-      <c r="P7" s="20" t="s">
-        <v>1138</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="R7" s="25" t="s">
-        <v>1114</v>
-      </c>
-      <c r="S7" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T7" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W7" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X7" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y7" s="14" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Z7" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA7" s="23" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB7" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC7" s="15" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AD7" s="23" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AE7" s="20" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AF7" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AG7" s="27" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AH7" s="25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AI7" s="25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AJ7" s="18" t="s">
-        <v>1125</v>
-      </c>
-      <c r="AK7" s="29" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AL7" s="28" t="s">
-        <v>1141</v>
-      </c>
-      <c r="AM7" s="26" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AN7" s="28" t="s">
-        <v>1147</v>
-      </c>
-      <c r="AO7" s="26" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="8" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N8" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>1137</v>
-      </c>
-      <c r="P8" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S8" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T8" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U8" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V8" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W8" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X8" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z8" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA8" s="31" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AB8" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC8" s="15" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AD8" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="AE8" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AF8" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AG8" s="29" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AH8" s="25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AI8" s="29" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AJ8" s="18" t="s">
-        <v>1125</v>
-      </c>
-      <c r="AK8" s="29" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AL8" s="18" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AM8" s="26" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AN8" s="18" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AO8" s="16" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="9" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>1137</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T9" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V9" s="17" t="s">
-        <v>1096</v>
-      </c>
-      <c r="W9" s="21" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X9" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Y9" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z9" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA9" s="31" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AB9" s="26" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AC9" s="15" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AD9" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="AE9" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AF9" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AG9" s="30" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AH9" s="13" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AI9" s="29" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AJ9" s="32" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AK9" s="30" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AL9" s="18" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AN9" s="29" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AO9" s="25" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="10" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="O10" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="R10" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S10" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T10" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="U10" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V10" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="W10" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="X10" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Y10" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z10" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA10" s="31" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AB10" s="28" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AC10" s="28" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AD10" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="AE10" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AF10" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AG10" s="30" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AH10" s="13" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AI10" s="29" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AJ10" s="32" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AK10" s="31" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AL10" s="30" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AM10" s="16" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AN10" s="30" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO10" s="13" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="11" spans="2:42" x14ac:dyDescent="0.2">
-      <c r="B11" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>1088</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>1089</v>
-      </c>
-      <c r="N11" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="R11" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>1119</v>
-      </c>
-      <c r="T11" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>1129</v>
-      </c>
-      <c r="V11" s="27" t="s">
-        <v>1171</v>
-      </c>
-      <c r="W11" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="X11" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Y11" s="31" t="s">
-        <v>1150</v>
-      </c>
-      <c r="Z11" s="28" t="s">
-        <v>1130</v>
-      </c>
-      <c r="AA11" s="31" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AB11" s="28" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AC11" s="28" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AD11" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="AE11" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AF11" s="29" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AG11" s="30" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AH11" s="30" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AI11" s="29" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AJ11" s="32" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AK11" s="31" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AL11" s="32" t="s">
-        <v>1172</v>
-      </c>
-      <c r="AM11" s="32" t="s">
-        <v>1172</v>
-      </c>
-      <c r="AN11" s="31" t="s">
-        <v>1173</v>
-      </c>
-      <c r="AO11" s="32" t="s">
-        <v>1174</v>
       </c>
     </row>
   </sheetData>

--- a/Entries HBC Premier Elite 2024.xlsx
+++ b/Entries HBC Premier Elite 2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sofienystrom/Badminton-Timetable-Solver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E02814-FDC4-CD48-AF21-2F15B1E459EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7CAF17-06A5-AE4F-9578-178F06731F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16680" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entries HBC Premier Elite 2024" sheetId="1" r:id="rId1"/>
@@ -3271,286 +3271,286 @@
     <t>WD C (8), WS C (5), WD B (3), WS B (3), MS C (9), MD C (8), MD B (2)</t>
   </si>
   <si>
+    <t>WD V - 1</t>
+  </si>
+  <si>
+    <t>MS A - 1</t>
+  </si>
+  <si>
+    <t>MS B - 1</t>
+  </si>
+  <si>
+    <t>WS V - 1</t>
+  </si>
+  <si>
+    <t>MD A - 1</t>
+  </si>
+  <si>
+    <t>XD V - 1</t>
+  </si>
+  <si>
+    <t>MS B - 2</t>
+  </si>
+  <si>
+    <t>XD V - 2</t>
+  </si>
+  <si>
+    <t>MS B - 3</t>
+  </si>
+  <si>
+    <t>MD V - 1</t>
+  </si>
+  <si>
+    <t>XD A - 1</t>
+  </si>
+  <si>
+    <t>MD V - 2</t>
+  </si>
+  <si>
+    <t>MD A - 2</t>
+  </si>
+  <si>
+    <t>MS V - 1</t>
+  </si>
+  <si>
+    <t>XD B - 1</t>
+  </si>
+  <si>
+    <t>XD A - 2</t>
+  </si>
+  <si>
+    <t>MS V - 2</t>
+  </si>
+  <si>
+    <t>MS C - 1</t>
+  </si>
+  <si>
+    <t>MS A - 2</t>
+  </si>
+  <si>
+    <t>XD A - 3</t>
+  </si>
+  <si>
+    <t>WS V - 2</t>
+  </si>
+  <si>
+    <t>MS A - 3</t>
+  </si>
+  <si>
+    <t>WD A - 2</t>
+  </si>
+  <si>
+    <t>XD V - 3</t>
+  </si>
+  <si>
+    <t>XD B - 2</t>
+  </si>
+  <si>
+    <t>WS B - 1</t>
+  </si>
+  <si>
+    <t>MD A - 4</t>
+  </si>
+  <si>
+    <t>XD B - 3</t>
+  </si>
+  <si>
+    <t>XD V - 4</t>
+  </si>
+  <si>
+    <t>WS B - 2</t>
+  </si>
+  <si>
+    <t>MD V - 4</t>
+  </si>
+  <si>
+    <t>WS A - 1</t>
+  </si>
+  <si>
+    <t>MS V - 3</t>
+  </si>
+  <si>
+    <t>XD B - 4</t>
+  </si>
+  <si>
+    <t>MD A - 5</t>
+  </si>
+  <si>
+    <t>MD B - 4</t>
+  </si>
+  <si>
+    <t>WS V - 3</t>
+  </si>
+  <si>
+    <t>MD B - 5</t>
+  </si>
+  <si>
+    <t>MS V - 4</t>
+  </si>
+  <si>
+    <t>MS B - 5</t>
+  </si>
+  <si>
+    <t>MS V - 5</t>
+  </si>
+  <si>
+    <t>MS B - 6</t>
+  </si>
+  <si>
+    <t>XD V - 5</t>
+  </si>
+  <si>
+    <t>XD B - 5</t>
+  </si>
+  <si>
+    <t>WD V - 2</t>
+  </si>
+  <si>
+    <t>MD V - 3</t>
+  </si>
+  <si>
+    <t>MS B - 4</t>
+  </si>
+  <si>
+    <t>WD A - 4</t>
+  </si>
+  <si>
+    <t>WD B - 4</t>
+  </si>
+  <si>
+    <t>WS V - 5</t>
+  </si>
+  <si>
+    <t>WS B - 4</t>
+  </si>
+  <si>
+    <t>XD A - 5</t>
+  </si>
+  <si>
+    <t>XD C - 1</t>
+  </si>
+  <si>
+    <t>WD A - 3</t>
+  </si>
+  <si>
+    <t>XD A - 4</t>
+  </si>
+  <si>
+    <t>WD V - 3</t>
+  </si>
+  <si>
+    <t>MS C - 4</t>
+  </si>
+  <si>
+    <t>WD B - 3</t>
+  </si>
+  <si>
+    <t>WS V - 4</t>
+  </si>
+  <si>
+    <t>WS B - 3</t>
+  </si>
+  <si>
+    <t>MS A - 6</t>
+  </si>
+  <si>
+    <t>WS C - 4</t>
+  </si>
+  <si>
+    <t>WS A - 4</t>
+  </si>
+  <si>
+    <t>MD C - 5</t>
+  </si>
+  <si>
+    <t>MD C - 1</t>
+  </si>
+  <si>
+    <t>MS C - 2</t>
+  </si>
+  <si>
+    <t>MD B - 1</t>
+  </si>
+  <si>
+    <t>XD C - 3</t>
+  </si>
+  <si>
+    <t>WS C - 2</t>
+  </si>
+  <si>
+    <t>MD B - 2</t>
+  </si>
+  <si>
+    <t>MS C - 3</t>
+  </si>
+  <si>
+    <t>WD V - 4</t>
+  </si>
+  <si>
+    <t>MD V - 5</t>
+  </si>
+  <si>
+    <t>MS A - 5</t>
+  </si>
+  <si>
+    <t>MS C - 6</t>
+  </si>
+  <si>
+    <t>XD C - 2</t>
+  </si>
+  <si>
     <t>WD B - 1</t>
   </si>
   <si>
-    <t>MS C - 1</t>
-  </si>
-  <si>
-    <t>MS C - 2</t>
-  </si>
-  <si>
-    <t>MS B - 1</t>
-  </si>
-  <si>
-    <t>MS B - 2</t>
-  </si>
-  <si>
-    <t>WD V - 1</t>
-  </si>
-  <si>
-    <t>XD A - 1</t>
-  </si>
-  <si>
-    <t>XD B - 1</t>
-  </si>
-  <si>
-    <t>MS V - 1</t>
-  </si>
-  <si>
-    <t>MS A - 1</t>
-  </si>
-  <si>
-    <t>XD V - 1</t>
-  </si>
-  <si>
-    <t>XD A - 2</t>
-  </si>
-  <si>
-    <t>WS V - 1</t>
-  </si>
-  <si>
-    <t>XD A - 3</t>
-  </si>
-  <si>
-    <t>MS A - 2</t>
-  </si>
-  <si>
-    <t>XD B - 3</t>
-  </si>
-  <si>
-    <t>MS A - 3</t>
-  </si>
-  <si>
-    <t>MD V - 1</t>
-  </si>
-  <si>
-    <t>MD A - 1</t>
-  </si>
-  <si>
-    <t>MD V - 2</t>
-  </si>
-  <si>
-    <t>MD A - 2</t>
-  </si>
-  <si>
-    <t>XD V - 2</t>
+    <t>MD C - 2</t>
+  </si>
+  <si>
+    <t>WD B - 2</t>
   </si>
   <si>
     <t>MD A - 3</t>
   </si>
   <si>
-    <t>XD V - 3</t>
-  </si>
-  <si>
-    <t>XD A - 4</t>
-  </si>
-  <si>
-    <t>MD A - 4</t>
-  </si>
-  <si>
-    <t>XD V - 4</t>
-  </si>
-  <si>
-    <t>XD B - 5</t>
-  </si>
-  <si>
-    <t>XD V - 5</t>
-  </si>
-  <si>
-    <t>WD V - 3</t>
-  </si>
-  <si>
-    <t>WD A - 3</t>
-  </si>
-  <si>
-    <t>MD V - 3</t>
-  </si>
-  <si>
-    <t>XD C - 2</t>
-  </si>
-  <si>
-    <t>MD V - 4</t>
-  </si>
-  <si>
-    <t>MS C - 3</t>
-  </si>
-  <si>
-    <t>WS V - 2</t>
-  </si>
-  <si>
-    <t>MD B - 4</t>
-  </si>
-  <si>
-    <t>MS V - 2</t>
-  </si>
-  <si>
-    <t>WS A - 1</t>
-  </si>
-  <si>
-    <t>MS B - 3</t>
-  </si>
-  <si>
-    <t>MS V - 3</t>
+    <t>MS A - 4</t>
   </si>
   <si>
     <t>WS A - 2</t>
   </si>
   <si>
-    <t>MS B - 5</t>
-  </si>
-  <si>
-    <t>MS V - 4</t>
-  </si>
-  <si>
-    <t>MS B - 6</t>
-  </si>
-  <si>
-    <t>MS V - 5</t>
-  </si>
-  <si>
-    <t>MD C - 1</t>
-  </si>
-  <si>
-    <t>MD B - 1</t>
-  </si>
-  <si>
-    <t>WD V - 2</t>
-  </si>
-  <si>
-    <t>XD A - 5</t>
-  </si>
-  <si>
-    <t>MD A - 5</t>
-  </si>
-  <si>
-    <t>WS B - 4</t>
-  </si>
-  <si>
-    <t>WS V - 5</t>
-  </si>
-  <si>
-    <t>XD B - 2</t>
+    <t>WS C - 3</t>
   </si>
   <si>
     <t>WD A - 1</t>
   </si>
   <si>
-    <t>WD A - 2</t>
-  </si>
-  <si>
-    <t>WD B - 2</t>
+    <t>WD C - 2</t>
+  </si>
+  <si>
+    <t>WS A - 3</t>
+  </si>
+  <si>
+    <t>MD B - 3</t>
+  </si>
+  <si>
+    <t>MD C - 3</t>
+  </si>
+  <si>
+    <t>MS C - 5</t>
+  </si>
+  <si>
+    <t>WD C - 1</t>
   </si>
   <si>
     <t>WS C - 1</t>
   </si>
   <si>
-    <t>WD A - 4</t>
-  </si>
-  <si>
-    <t>WD C - 2</t>
+    <t>MD C - 4</t>
+  </si>
+  <si>
+    <t>XD C - 4</t>
   </si>
   <si>
     <t>WD C - 3</t>
-  </si>
-  <si>
-    <t>MD B - 5</t>
-  </si>
-  <si>
-    <t>WS V - 3</t>
-  </si>
-  <si>
-    <t>WS B - 3</t>
-  </si>
-  <si>
-    <t>WS V - 4</t>
-  </si>
-  <si>
-    <t>MS A - 6</t>
-  </si>
-  <si>
-    <t>XD C - 1</t>
-  </si>
-  <si>
-    <t>MD B - 2</t>
-  </si>
-  <si>
-    <t>MD B - 3</t>
-  </si>
-  <si>
-    <t>WS C - 2</t>
-  </si>
-  <si>
-    <t>XD C - 3</t>
-  </si>
-  <si>
-    <t>WS A - 4</t>
-  </si>
-  <si>
-    <t>MD C - 3</t>
-  </si>
-  <si>
-    <t>MD C - 4</t>
-  </si>
-  <si>
-    <t>WD V - 4</t>
-  </si>
-  <si>
-    <t>MD V - 5</t>
-  </si>
-  <si>
-    <t>MS B - 4</t>
-  </si>
-  <si>
-    <t>MS A - 5</t>
-  </si>
-  <si>
-    <t>XD C - 4</t>
-  </si>
-  <si>
-    <t>WD C - 1</t>
-  </si>
-  <si>
-    <t>XD B - 4</t>
-  </si>
-  <si>
-    <t>WS B - 1</t>
-  </si>
-  <si>
-    <t>WD B - 3</t>
-  </si>
-  <si>
-    <t>MS A - 4</t>
-  </si>
-  <si>
-    <t>MD C - 2</t>
-  </si>
-  <si>
-    <t>WS A - 3</t>
-  </si>
-  <si>
-    <t>MS C - 4</t>
-  </si>
-  <si>
-    <t>WD B - 4</t>
-  </si>
-  <si>
-    <t>WS B - 2</t>
-  </si>
-  <si>
-    <t>MS C - 6</t>
-  </si>
-  <si>
-    <t>WS C - 3</t>
-  </si>
-  <si>
-    <t>WS C - 4</t>
-  </si>
-  <si>
-    <t>MS C - 5</t>
-  </si>
-  <si>
-    <t>MD C - 5</t>
   </si>
 </sst>
 </file>
@@ -3611,8 +3611,74 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF42A5F5"/>
+        <bgColor rgb="FF42A5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC407A"/>
+        <bgColor rgb="FFEC407A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66BB6A"/>
+        <bgColor rgb="FF66BB6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90CAF9"/>
+        <bgColor rgb="FF90CAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF64B5F6"/>
         <bgColor rgb="FF64B5F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE082"/>
+        <bgColor rgb="FFFFE082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE0E0"/>
+        <bgColor rgb="FFFDE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF06292"/>
+        <bgColor rgb="FFF06292"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81C784"/>
+        <bgColor rgb="FF81C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5D6A7"/>
+        <bgColor rgb="FFA5D6A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBDEFB"/>
+        <bgColor rgb="FFBBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+        <bgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -3623,38 +3689,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE0E0"/>
-        <bgColor rgb="FFFDE0E0"/>
+        <fgColor rgb="FFFFD54F"/>
+        <bgColor rgb="FFFFD54F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBDEFB"/>
-        <bgColor rgb="FFBBDEFB"/>
+        <fgColor rgb="FFFFF8E1"/>
+        <bgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5D6A7"/>
-        <bgColor rgb="FFA5D6A7"/>
+        <fgColor rgb="FFFFECB3"/>
+        <bgColor rgb="FFFFECB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF42A5F5"/>
-        <bgColor rgb="FF42A5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90CAF9"/>
-        <bgColor rgb="FF90CAF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66BB6A"/>
-        <bgColor rgb="FF66BB6A"/>
+        <fgColor rgb="FFF48FB1"/>
+        <bgColor rgb="FFF48FB1"/>
       </patternFill>
     </fill>
     <fill>
@@ -3665,68 +3719,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F2FD"/>
-        <bgColor rgb="FFE3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC407A"/>
-        <bgColor rgb="FFEC407A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF06292"/>
-        <bgColor rgb="FFF06292"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
-        <bgColor rgb="FFFFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81C784"/>
-        <bgColor rgb="FF81C784"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE082"/>
-        <bgColor rgb="FFFFE082"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD54F"/>
-        <bgColor rgb="FFFFD54F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFECB3"/>
-        <bgColor rgb="FFFFECB3"/>
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8BBD0"/>
         <bgColor rgb="FFF8BBD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF48FB1"/>
-        <bgColor rgb="FFF48FB1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E6C9"/>
-        <bgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -3780,24 +3780,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -18966,8 +18966,8 @@
     <col min="1" max="1" width="29.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="8.83203125" style="7" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="7"/>
+    <col min="4" max="12" width="8.83203125" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -22861,1237 +22861,1237 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B2:BB13"/>
+  <dimension ref="B2:BA13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:54" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B2" s="13" t="s">
         <v>1086</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>1090</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U2" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X2" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y2" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z2" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AB2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AC2" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD2" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF2" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AH2" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI2" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK2" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AL2" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM2" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN2" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AO2" s="23" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP2" s="20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AQ2" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AS2" s="26" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AU2" s="23" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AV2" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AW2" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AX2" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AY2" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AZ2" s="19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BA2" s="16" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="3" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
         <v>1086</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="C3" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U3" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X3" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y3" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z3" s="19" t="s">
         <v>1084</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="AB3" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG3" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AH3" s="18" t="s">
         <v>1093</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="AI3" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK3" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AL3" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM3" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AO3" s="23" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP3" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ3" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR3" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AS3" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT3" s="14" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AV3" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AW3" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AX3" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AY3" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
+        <v>1143</v>
+      </c>
+      <c r="BA3" s="28" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="4" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B4" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q4" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V4" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X4" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z4" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC4" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="AD4" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE4" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF4" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG4" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH4" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI4" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ4" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK4" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AL4" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM4" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN4" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AP4" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ4" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR4" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AS4" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT4" s="30" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AV4" s="17" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AW4" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX4" s="15" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AY4" s="28" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AZ4" s="18" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="5" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B5" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>1085</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="L5" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q5" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U5" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V5" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X5" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z5" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB5" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC5" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD5" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE5" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF5" s="21" t="s">
         <v>1102</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="AG5" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH5" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI5" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AJ5" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK5" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AL5" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM5" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN5" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AP5" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ5" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR5" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AS5" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV5" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW5" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX5" s="25" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AY5" s="28" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="6" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B6" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q6" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U6" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V6" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X6" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z6" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB6" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC6" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF6" s="21" t="s">
         <v>1102</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N2" s="19" t="s">
+      <c r="AG6" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH6" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI6" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AJ6" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AK6" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AL6" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM6" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AN6" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP6" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AQ6" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AR6" s="30" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AS6" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV6" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW6" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX6" s="25" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AZ6" s="32" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B7" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q7" s="22" t="s">
         <v>1098</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="R7" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U7" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V7" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X7" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Y7" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z7" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC7" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF7" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG7" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH7" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI7" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AJ7" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AK7" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AL7" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM7" s="24" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AN7" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP7" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ7" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AR7" s="30" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AS7" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV7" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW7" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX7" s="22" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D8" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>1087</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="H8" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q8" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R8" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>1100</v>
       </c>
-      <c r="Q2" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R2" s="21" t="s">
+      <c r="U8" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V8" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X8" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Y8" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z8" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB8" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC8" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF8" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG8" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH8" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI8" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="S2" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T2" s="21" t="s">
+      <c r="AK8" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL8" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM8" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AN8" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP8" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ8" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AS8" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV8" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AX8" s="22" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="9" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D9" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R9" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U9" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V9" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Y9" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z9" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB9" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC9" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF9" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG9" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH9" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI9" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="U2" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W2" s="23" t="s">
+      <c r="AK9" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL9" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AM9" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AN9" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP9" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ9" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AS9" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AX9" s="32" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="10" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D10" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M10" s="21" t="s">
         <v>1082</v>
       </c>
-      <c r="X2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z2" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD2" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AE2" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF2" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG2" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI2" s="25" t="s">
+      <c r="O10" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R10" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="U10" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V10" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y10" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z10" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB10" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC10" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF10" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AG10" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH10" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI10" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AK10" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL10" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN10" s="31" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AP10" s="25" t="s">
         <v>1162</v>
       </c>
-      <c r="AJ2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AQ10" s="28" t="s">
         <v>1106</v>
       </c>
-      <c r="AL2" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM2" s="18" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AN2" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AP2" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ2" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AR2" s="22" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AT2" s="27" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AU2" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AV2" s="27" t="s">
-        <v>1142</v>
-      </c>
-      <c r="AW2" s="21" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AX2" s="15" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AY2" s="21" t="s">
-        <v>1126</v>
-      </c>
-      <c r="AZ2" s="15" t="s">
-        <v>1125</v>
-      </c>
-      <c r="BA2" s="18" t="s">
-        <v>1109</v>
-      </c>
-      <c r="BB2" s="22" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="3" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C3" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="AS10" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AX10" s="32" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="11" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="G11" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R11" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V11" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y11" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z11" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB11" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC11" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="AF11" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH11" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI11" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AK11" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL11" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN11" s="31" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AP11" s="31" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AQ11" s="28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="12" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="H12" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R12" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V12" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AB12" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC12" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="H3" s="18" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="AF12" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH12" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI12" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AL12" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AQ12" s="28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="H13" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>1085</v>
       </c>
-      <c r="J3" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>1087</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="S3" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T3" s="21" t="s">
+      <c r="O13" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R13" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V13" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AB13" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC13" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AF13" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH13" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI13" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="U3" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Y3" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z3" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA3" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC3" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE3" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF3" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG3" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI3" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AL3" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM3" s="18" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AN3" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO3" s="19" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AP3" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ3" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AR3" s="22" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AS3" s="24" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AT3" s="27" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AU3" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AV3" s="28" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AW3" s="21" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AX3" s="15" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AY3" s="16" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AZ3" s="25" t="s">
-        <v>1132</v>
-      </c>
-      <c r="BA3" s="20" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="4" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C4" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>1087</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q4" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="S4" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T4" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U4" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W4" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X4" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y4" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z4" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA4" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD4" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE4" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG4" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH4" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI4" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ4" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AK4" s="24" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AL4" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM4" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AN4" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO4" s="13" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AP4" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ4" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AS4" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AT4" s="28" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AU4" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AW4" s="16" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AX4" s="25" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AY4" s="14" t="s">
-        <v>1146</v>
-      </c>
-      <c r="BA4" s="30" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="5" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C5" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="S5" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T5" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U5" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V5" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X5" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y5" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z5" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA5" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB5" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD5" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE5" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF5" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG5" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH5" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI5" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ5" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AK5" s="24" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AL5" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM5" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AN5" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO5" s="13" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AP5" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AS5" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AU5" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AW5" s="16" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AX5" s="25" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AY5" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="BA5" s="31" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="6" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C6" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U6" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V6" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W6" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X6" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y6" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z6" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB6" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC6" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD6" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE6" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF6" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG6" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH6" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI6" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ6" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AM6" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN6" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO6" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP6" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ6" s="13" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AS6" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU6" s="19" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AW6" s="14" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AY6" s="23" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="7" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D7" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T7" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U7" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V7" s="28" t="s">
-        <v>1081</v>
-      </c>
-      <c r="W7" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X7" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y7" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z7" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB7" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD7" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE7" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF7" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG7" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH7" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI7" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ7" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AK7" s="29" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AM7" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN7" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO7" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP7" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ7" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS7" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU7" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW7" s="14" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AY7" s="30" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="8" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D8" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R8" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T8" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U8" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V8" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W8" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X8" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y8" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z8" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB8" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD8" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE8" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF8" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG8" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH8" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI8" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ8" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM8" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN8" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO8" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP8" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ8" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS8" s="32" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AU8" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW8" s="26" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AY8" s="30" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="9" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D9" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R9" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T9" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U9" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V9" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X9" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y9" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z9" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB9" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD9" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE9" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF9" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG9" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH9" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ9" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM9" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN9" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO9" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP9" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ9" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS9" s="32" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AU9" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW9" s="26" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="10" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D10" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T10" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="V10" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W10" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X10" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y10" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z10" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB10" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC10" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD10" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE10" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF10" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH10" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ10" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM10" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN10" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP10" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ10" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AU10" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW10" s="23" t="s">
+      <c r="AL13" s="29" t="s">
         <v>1173</v>
-      </c>
-    </row>
-    <row r="11" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D11" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="W11" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X11" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC11" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD11" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE11" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF11" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH11" s="30" t="s">
-        <v>1138</v>
-      </c>
-      <c r="AI11" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ11" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM11" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN11" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO11" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP11" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ11" s="31" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AU11" s="29" t="s">
-        <v>1159</v>
-      </c>
-      <c r="AW11" s="23" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="12" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D12" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="W12" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y12" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC12" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD12" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE12" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF12" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH12" s="30" t="s">
-        <v>1138</v>
-      </c>
-      <c r="AJ12" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM12" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN12" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO12" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP12" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ12" s="31" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AW12" s="32" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="13" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D13" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="W13" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X13" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC13" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD13" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE13" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF13" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AJ13" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM13" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN13" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO13" s="23" t="s">
-        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -24101,1237 +24101,1237 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:BB13"/>
+  <dimension ref="B2:BA13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:54" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B2" s="13" t="s">
         <v>1086</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>1090</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U2" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X2" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y2" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z2" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AB2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AC2" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD2" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF2" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG2" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AH2" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI2" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK2" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AL2" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM2" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN2" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AO2" s="23" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP2" s="20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AQ2" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AS2" s="26" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AU2" s="23" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AV2" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AW2" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AX2" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AY2" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AZ2" s="19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BA2" s="16" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="3" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
         <v>1086</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="C3" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U3" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X3" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y3" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z3" s="19" t="s">
         <v>1084</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="AB3" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG3" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AH3" s="18" t="s">
         <v>1093</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="AI3" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK3" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AL3" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM3" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AO3" s="23" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AP3" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ3" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR3" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AS3" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT3" s="14" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AV3" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AW3" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AX3" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AY3" s="16" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
+        <v>1143</v>
+      </c>
+      <c r="BA3" s="28" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="4" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B4" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q4" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V4" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X4" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z4" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC4" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="AD4" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE4" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF4" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG4" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH4" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI4" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AJ4" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK4" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AL4" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM4" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN4" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AP4" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ4" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR4" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AS4" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AT4" s="30" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AV4" s="17" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AW4" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX4" s="15" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AY4" s="28" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AZ4" s="18" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="5" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B5" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>1085</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="L5" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q5" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="U5" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V5" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X5" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z5" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB5" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC5" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AD5" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE5" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF5" s="21" t="s">
         <v>1102</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="AG5" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH5" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI5" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AJ5" s="21" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AK5" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AL5" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM5" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN5" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AP5" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AQ5" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AR5" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AS5" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV5" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW5" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX5" s="25" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AY5" s="28" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="6" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B6" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Q6" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U6" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V6" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X6" s="27" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z6" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB6" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AC6" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AF6" s="21" t="s">
         <v>1102</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N2" s="19" t="s">
+      <c r="AG6" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AH6" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI6" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AJ6" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AK6" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AL6" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM6" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AN6" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP6" s="21" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AQ6" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AR6" s="30" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AS6" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV6" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW6" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX6" s="25" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AZ6" s="32" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B7" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q7" s="22" t="s">
         <v>1098</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="R7" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U7" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V7" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X7" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Y7" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z7" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC7" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF7" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG7" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH7" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI7" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AJ7" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AK7" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AL7" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM7" s="24" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AN7" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP7" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ7" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AR7" s="30" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AS7" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV7" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AW7" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AX7" s="22" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D8" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>1087</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="H8" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q8" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R8" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>1100</v>
       </c>
-      <c r="Q2" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R2" s="21" t="s">
+      <c r="U8" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V8" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X8" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Y8" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z8" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB8" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC8" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF8" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG8" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH8" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI8" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="S2" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T2" s="21" t="s">
+      <c r="AK8" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL8" s="25" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AM8" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AN8" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP8" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ8" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AS8" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AV8" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AX8" s="22" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="9" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D9" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="R9" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="U9" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V9" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Y9" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z9" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB9" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC9" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF9" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AG9" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH9" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AI9" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="U2" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W2" s="23" t="s">
+      <c r="AK9" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL9" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AM9" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AN9" s="32" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AP9" s="25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AQ9" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AS9" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AX9" s="32" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="10" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="D10" s="31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M10" s="21" t="s">
         <v>1082</v>
       </c>
-      <c r="X2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z2" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD2" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AE2" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF2" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG2" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI2" s="25" t="s">
+      <c r="O10" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R10" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="U10" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="V10" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y10" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z10" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB10" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC10" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AF10" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AG10" s="24" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AH10" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI10" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AK10" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL10" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN10" s="31" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AP10" s="25" t="s">
         <v>1162</v>
       </c>
-      <c r="AJ2" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AQ10" s="28" t="s">
         <v>1106</v>
       </c>
-      <c r="AL2" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM2" s="18" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AN2" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AP2" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ2" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AR2" s="22" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AT2" s="27" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AU2" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AV2" s="27" t="s">
-        <v>1142</v>
-      </c>
-      <c r="AW2" s="21" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AX2" s="15" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AY2" s="21" t="s">
-        <v>1126</v>
-      </c>
-      <c r="AZ2" s="15" t="s">
-        <v>1125</v>
-      </c>
-      <c r="BA2" s="18" t="s">
-        <v>1109</v>
-      </c>
-      <c r="BB2" s="22" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="3" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C3" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="AS10" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AX10" s="32" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="11" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="G11" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R11" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V11" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y11" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z11" s="29" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB11" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC11" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="AF11" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH11" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI11" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AK11" s="26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AL11" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AN11" s="31" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AP11" s="31" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AQ11" s="28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="12" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="H12" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R12" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V12" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AB12" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC12" s="21" t="s">
         <v>1099</v>
       </c>
-      <c r="H3" s="18" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="AF12" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH12" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI12" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AL12" s="18" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AQ12" s="28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="H13" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>1085</v>
       </c>
-      <c r="J3" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>1087</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="S3" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T3" s="21" t="s">
+      <c r="O13" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R13" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="V13" s="22" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AB13" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AC13" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AF13" s="31" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AH13" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AI13" s="16" t="s">
         <v>1089</v>
       </c>
-      <c r="U3" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="Y3" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z3" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA3" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC3" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE3" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF3" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG3" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI3" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AL3" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM3" s="18" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AN3" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO3" s="19" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AP3" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ3" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AR3" s="22" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AS3" s="24" t="s">
-        <v>1139</v>
-      </c>
-      <c r="AT3" s="27" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AU3" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AV3" s="28" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AW3" s="21" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AX3" s="15" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AY3" s="16" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AZ3" s="25" t="s">
-        <v>1132</v>
-      </c>
-      <c r="BA3" s="20" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="4" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C4" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>1087</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q4" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="S4" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T4" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U4" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W4" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X4" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y4" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z4" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA4" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD4" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE4" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG4" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH4" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI4" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ4" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AK4" s="24" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AL4" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM4" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AN4" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO4" s="13" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AP4" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ4" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AS4" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AT4" s="28" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AU4" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AW4" s="16" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AX4" s="25" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AY4" s="14" t="s">
-        <v>1146</v>
-      </c>
-      <c r="BA4" s="30" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="5" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C5" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="S5" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T5" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U5" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V5" s="21" t="s">
-        <v>1118</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X5" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y5" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z5" s="19" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AA5" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AB5" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD5" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE5" s="24" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AF5" s="18" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AG5" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH5" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI5" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ5" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AK5" s="24" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AL5" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AM5" s="20" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AN5" s="25" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AO5" s="13" t="s">
-        <v>1110</v>
-      </c>
-      <c r="AP5" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AS5" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AU5" s="16" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AW5" s="16" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AX5" s="25" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AY5" s="26" t="s">
-        <v>1152</v>
-      </c>
-      <c r="BA5" s="31" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="6" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="C6" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>1102</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>1129</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U6" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V6" s="16" t="s">
-        <v>1093</v>
-      </c>
-      <c r="W6" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X6" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y6" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z6" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB6" s="19" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AC6" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD6" s="15" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AE6" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF6" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG6" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH6" s="16" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AI6" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ6" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AM6" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN6" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO6" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP6" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ6" s="13" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AS6" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU6" s="19" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AW6" s="14" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AY6" s="23" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="7" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D7" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T7" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U7" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V7" s="28" t="s">
-        <v>1081</v>
-      </c>
-      <c r="W7" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X7" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Y7" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z7" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB7" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD7" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE7" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF7" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG7" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH7" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI7" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ7" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AK7" s="29" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AM7" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN7" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO7" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP7" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ7" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS7" s="23" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU7" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW7" s="14" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AY7" s="30" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="8" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D8" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R8" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T8" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U8" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V8" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W8" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X8" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y8" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z8" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB8" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD8" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE8" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF8" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG8" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH8" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI8" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AJ8" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM8" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN8" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO8" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP8" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="AQ8" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS8" s="32" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AU8" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW8" s="26" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AY8" s="30" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="9" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D9" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>1101</v>
-      </c>
-      <c r="R9" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T9" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="U9" s="20" t="s">
-        <v>1092</v>
-      </c>
-      <c r="V9" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X9" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y9" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z9" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB9" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AD9" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE9" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF9" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AG9" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AH9" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ9" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM9" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AN9" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO9" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP9" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ9" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AS9" s="32" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AU9" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW9" s="26" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="10" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D10" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="T10" s="29" t="s">
-        <v>1113</v>
-      </c>
-      <c r="V10" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="W10" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X10" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y10" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="Z10" s="31" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB10" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AC10" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD10" s="28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AE10" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF10" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH10" s="17" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ10" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM10" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN10" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP10" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ10" s="14" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AU10" s="26" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AW10" s="23" t="s">
+      <c r="AL13" s="29" t="s">
         <v>1173</v>
-      </c>
-    </row>
-    <row r="11" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D11" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>1147</v>
-      </c>
-      <c r="W11" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X11" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC11" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD11" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE11" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF11" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH11" s="30" t="s">
-        <v>1138</v>
-      </c>
-      <c r="AI11" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AJ11" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM11" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN11" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO11" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP11" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ11" s="31" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AU11" s="29" t="s">
-        <v>1159</v>
-      </c>
-      <c r="AW11" s="23" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="12" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D12" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="W12" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y12" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC12" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD12" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE12" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF12" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AH12" s="30" t="s">
-        <v>1138</v>
-      </c>
-      <c r="AJ12" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM12" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN12" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO12" s="23" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP12" s="27" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AQ12" s="31" t="s">
-        <v>1154</v>
-      </c>
-      <c r="AW12" s="32" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="13" spans="2:54" x14ac:dyDescent="0.2">
-      <c r="D13" s="14" t="s">
-        <v>1090</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="W13" s="23" t="s">
-        <v>1082</v>
-      </c>
-      <c r="X13" s="24" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC13" s="31" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AD13" s="32" t="s">
-        <v>1160</v>
-      </c>
-      <c r="AE13" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AF13" s="23" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AJ13" s="27" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AM13" s="31" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AN13" s="27" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AO13" s="23" t="s">
-        <v>1115</v>
       </c>
     </row>
   </sheetData>
